--- a/checklist_forms/045_pre_delivery_inspection_form--checklist_forms.xlsx
+++ b/checklist_forms/045_pre_delivery_inspection_form--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -964,8 +964,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'gasoline',_'value':_'gasoline'}</t>
+          <t>gasoline</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Gasoline', 'value': 'Gasoline'}</t>
+          <t>Gasoline</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'electric',_'value':_'electric'}</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Electric', 'value': 'Electric'}</t>
+          <t>Electric</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'hybrid',_'value':_'hybrid'}</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Hybrid', 'value': 'Hybrid'}</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'full',_'value':_'full'}</t>
+          <t>full</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Full', 'value': 'Full'}</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'quarter',_'value':_'quarter'}</t>
+          <t>quarter</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Quarter', 'value': 'Quarter'}</t>
+          <t>Quarter</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'empty',_'value':_'empty'}</t>
+          <t>empty</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Empty', 'value': 'Empty'}</t>
+          <t>Empty</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'clean',_'value':_'clean'}</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Clean', 'value': 'Clean'}</t>
+          <t>Clean</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'stains',_'value':_'stains'}</t>
+          <t>stains</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Stains', 'value': 'Stains'}</t>
+          <t>Stains</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'dents',_'value':_'dents'}</t>
+          <t>dents</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Dents', 'value': 'Dents'}</t>
+          <t>Dents</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'clean',_'value':_'clean'}</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Clean', 'value': 'Clean'}</t>
+          <t>Clean</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'stains',_'value':_'stains'}</t>
+          <t>stains</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Stains', 'value': 'Stains'}</t>
+          <t>Stains</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'odor',_'value':_'odor'}</t>
+          <t>odor</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Odor', 'value': 'Odor'}</t>
+          <t>Odor</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'automatic',_'value':_'automatic'}</t>
+          <t>automatic</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Automatic', 'value': 'Automatic'}</t>
+          <t>Automatic</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'manual',_'value':_'manual'}</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Manual', 'value': 'Manual'}</t>
+          <t>Manual</t>
         </is>
       </c>
     </row>
